--- a/event_planner_forms/007_event_interest_form--event_planner_forms.xlsx
+++ b/event_planner_forms/007_event_interest_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>preferred_time</t>
+          <t>preferred_time_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Preferred Time</t>
+          <t>Preferred Time 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>preferred_time_2</t>
+          <t>preferred_time_2_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Preferred Time</t>
+          <t>Preferred Time 2 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Preferred Day</t>
+          <t>Preferred Day 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other Info</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>preferred_time_choices</t>
+          <t>preferred_time_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>preferred_time_choices</t>
+          <t>preferred_time_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>preferred_time_choices</t>
+          <t>preferred_time_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>preferred_time_2_choices</t>
+          <t>preferred_time_2_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>preferred_time_2_choices</t>
+          <t>preferred_time_2_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>preferred_time_2_choices</t>
+          <t>preferred_time_2_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
